--- a/Proyectos/Analytics_Chatbot/Latinoamerica.xlsx
+++ b/Proyectos/Analytics_Chatbot/Latinoamerica.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10517"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4408440-D81A-5C41-AE5A-D9BAF04B26BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94656B14-F80F-0D4F-B550-5D30D1F0366E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="19440" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="31700" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paises" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paises!$A$1:$A$53</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1187,6 +1190,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>